--- a/references/formatted-charts.xlsx
+++ b/references/formatted-charts.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhhc/Code/agentic-architecture/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27396D74-58E3-8F49-BBFC-3972E6FEB624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4A106A-9138-E942-AA7B-244A31CD6265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="69440" yWindow="5140" windowWidth="32740" windowHeight="21540" xr2:uid="{0314D787-E6D8-024C-BE9C-BB2C2F50E854}"/>
+    <workbookView xWindow="60900" yWindow="880" windowWidth="32760" windowHeight="27600" activeTab="1" xr2:uid="{0314D787-E6D8-024C-BE9C-BB2C2F50E854}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Archetypes - Features" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="84">
   <si>
     <t>F1</t>
   </si>
@@ -189,13 +190,161 @@
   </si>
   <si>
     <t>13. Conversational Agent</t>
+  </si>
+  <si>
+    <r>
+      <t>Legend</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>: ● Required | ◐ Often Needed | ○ Optional | − Not Applicable</t>
+    </r>
+  </si>
+  <si>
+    <t>Foundation Models (§1.1)</t>
+  </si>
+  <si>
+    <t>Prompting (§1.2)</t>
+  </si>
+  <si>
+    <t>RAG &amp; Retrieval (§2.1)</t>
+  </si>
+  <si>
+    <t>Output Processing (§2.2)</t>
+  </si>
+  <si>
+    <t>Context Management (§3.1)</t>
+  </si>
+  <si>
+    <t>Memory Systems (§3.2)</t>
+  </si>
+  <si>
+    <t>Reasoning &amp; Planning (§3.3)</t>
+  </si>
+  <si>
+    <t>Tool Use &amp; Functions (§3.4)</t>
+  </si>
+  <si>
+    <t>Agentic Architectures (§4.1)</t>
+  </si>
+  <si>
+    <t>Workflow Orchestration (§4.2)</t>
+  </si>
+  <si>
+    <t>HITL Patterns (§4.3)</t>
+  </si>
+  <si>
+    <t>Safety &amp; Guardrails (§5.1)</t>
+  </si>
+  <si>
+    <t>Evaluation &amp; Testing (§5.2)</t>
+  </si>
+  <si>
+    <t>Observability &amp; Infrastructure (§5.3–5.4)</t>
+  </si>
+  <si>
+    <t>F1: Contextual Grounding</t>
+  </si>
+  <si>
+    <t>F2: Multi-Source Synthesis</t>
+  </si>
+  <si>
+    <t>F3: Structured Output</t>
+  </si>
+  <si>
+    <t>F4: Interactive Refinement</t>
+  </si>
+  <si>
+    <t>F5: Citation &amp; Provenance</t>
+  </si>
+  <si>
+    <t>F6: Adaptive Personalization</t>
+  </si>
+  <si>
+    <t>F7: Autonomous Planning</t>
+  </si>
+  <si>
+    <t>F8: Tool Orchestration</t>
+  </si>
+  <si>
+    <t>F9: Real-Time Data Access</t>
+  </si>
+  <si>
+    <t>F10: Long-Term Memory</t>
+  </si>
+  <si>
+    <t>F11: Human Oversight Gates</t>
+  </si>
+  <si>
+    <t>F12: Safety &amp; Content Controls</t>
+  </si>
+  <si>
+    <t>F13: Learning &amp; Feedback</t>
+  </si>
+  <si>
+    <t>F14: Multi-Agent Collaboration</t>
+  </si>
+  <si>
+    <t>F15: Auditability &amp; Compliance</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>§1.3 Model Selection &amp; Customization Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Underpins all features — model capability and adaptation approach (the customization ladder) set the performance ceiling for every feature in the stack. Evaluate before finalising any other component choice.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>§4.4 Agent Runtime &amp; Deployment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Production infrastructure prerequisite for F7 (Autonomous Planning) and F14 (Multi-Agent Collaboration). Any T3/T4 deployment that includes these features requires a hosting pattern, session lifecycle management, and compute isolation.</t>
+    </r>
+  </si>
+  <si>
+    <t>Features</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -228,6 +377,39 @@
       <color theme="2"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -262,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -283,12 +465,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -297,6 +473,28 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -632,11 +830,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE776E8-A382-3B42-B43B-05BA02638930}">
-  <dimension ref="B2:Q19"/>
+  <dimension ref="B2:Q21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="5" style="7" customWidth="1"/>
+    <col min="3" max="17" width="6.1640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="20" x14ac:dyDescent="0.2">
@@ -690,71 +888,71 @@
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
     </row>
     <row r="5" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -807,52 +1005,52 @@
       </c>
     </row>
     <row r="6" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="12" t="s">
+      <c r="C6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q6" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -907,74 +1105,74 @@
       </c>
     </row>
     <row r="8" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q8" s="12" t="s">
+      <c r="C8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q8" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
     </row>
     <row r="10" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
@@ -1027,52 +1225,52 @@
       </c>
     </row>
     <row r="11" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="12" t="s">
+      <c r="C11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1127,30 +1325,32 @@
       </c>
     </row>
     <row r="13" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
     </row>
     <row r="14" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="D14" s="6" t="s">
         <v>37</v>
       </c>
@@ -1195,52 +1395,52 @@
       </c>
     </row>
     <row r="15" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15" s="11" t="s">
+      <c r="C15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q15" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1295,52 +1495,52 @@
       </c>
     </row>
     <row r="17" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P17" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q17" s="11" t="s">
+      <c r="C17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1395,53 +1595,58 @@
       </c>
     </row>
     <row r="19" spans="2:17" s="3" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>37</v>
+      <c r="C19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B21" s="12" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1452,4 +1657,843 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6117A06B-78CF-1144-8831-9866BB379051}">
+  <dimension ref="B2:P24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="43.5" customWidth="1"/>
+    <col min="3" max="16" width="6" style="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" ht="312" x14ac:dyDescent="0.2">
+      <c r="C2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+    </row>
+    <row r="4" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" s="3" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="23" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="2:16" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+    </row>
+    <row r="22" spans="2:16" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+    </row>
+    <row r="23" spans="2:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="B23" s="1"/>
+      <c r="C23" s="17"/>
+    </row>
+    <row r="24" spans="2:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:P3"/>
+    <mergeCell ref="B21:P21"/>
+    <mergeCell ref="B22:P22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>